--- a/artfynd/A 51785-2025 artfynd.xlsx
+++ b/artfynd/A 51785-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74528316</v>
       </c>
       <c r="B2" t="n">
-        <v>99181</v>
+        <v>99191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51785-2025 artfynd.xlsx
+++ b/artfynd/A 51785-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74528316</v>
+        <v>74500801</v>
       </c>
       <c r="B2" t="n">
-        <v>99191</v>
+        <v>97534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222541</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Juncus squarrosus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nyatorp 500 m N, Sm</t>
+          <t>Nyatorp 450 m N, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475670</v>
+        <v>475771</v>
       </c>
       <c r="R2" t="n">
-        <v>6293987</v>
+        <v>6293889</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -740,17 +736,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1991-01-01</t>
+          <t>1981-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1991-12-31</t>
+          <t>1989-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4E9f 1414. SOM: Juncus squarrosus. LEG: Curt Mossberg, Stig Johnsson</t>
+          <t>Smålands flora 2007: KOO: 4E9f 1315. SOM: Huperzia selago. LEG: Stig Johnsson, Curt Mossberg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,6 +770,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>74528316</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222541</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Borsttåg</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Juncus squarrosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nyatorp 500 m N, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>475670</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6293987</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skatelöv</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1991-01-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1991-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 4E9f 1414. SOM: Juncus squarrosus. LEG: Curt Mossberg, Stig Johnsson</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 51785-2025 artfynd.xlsx
+++ b/artfynd/A 51785-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74500801</v>
       </c>
       <c r="B2" t="n">
-        <v>97534</v>
+        <v>97977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>74528316</v>
       </c>
       <c r="B3" t="n">
-        <v>99191</v>
+        <v>99646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51785-2025 artfynd.xlsx
+++ b/artfynd/A 51785-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74500801</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,8 +890,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74528316</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>